--- a/서버정보/20260617_리소스배포_운영_2차배포.xlsx
+++ b/서버정보/20260617_리소스배포_운영_2차배포.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D87C497-BBCA-43BE-871C-527F298E3E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D432F283-26FD-4E84-B1C8-92D2625B889E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7370" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7368" uniqueCount="1114">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5578,10 +5578,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-dtg-cdmlap-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5732,6 +5728,14 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8842,10 +8846,7 @@
       <c r="B2" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="82" t="str" cm="1">
-        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C2" s="82"/>
       <c r="D2" s="82" t="s">
         <v>1008</v>
       </c>
@@ -8904,10 +8905,7 @@
       <c r="B3" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="74" t="str" cm="1">
-        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C3" s="74"/>
       <c r="D3" s="74" t="s">
         <v>1008</v>
       </c>
@@ -8966,10 +8964,7 @@
       <c r="B4" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="82" t="str" cm="1">
-        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($D4, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C4" s="82"/>
       <c r="D4" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9028,10 +9023,7 @@
       <c r="B5" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="74" t="str" cm="1">
-        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C5" s="74"/>
       <c r="D5" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9090,10 +9082,7 @@
       <c r="B6" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="74" t="str" cm="1">
-        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C6" s="74"/>
       <c r="D6" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9152,10 +9141,7 @@
       <c r="B7" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="74" t="str" cm="1">
-        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C7" s="74"/>
       <c r="D7" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9214,10 +9200,7 @@
       <c r="B8" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="82" t="str" cm="1">
-        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C8" s="82"/>
       <c r="D8" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9276,10 +9259,7 @@
       <c r="B9" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="74" t="str" cm="1">
-        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C9" s="74"/>
       <c r="D9" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9338,10 +9318,7 @@
       <c r="B10" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="82" t="str" cm="1">
-        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C10" s="82"/>
       <c r="D10" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9400,10 +9377,7 @@
       <c r="B11" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="74" t="str" cm="1">
-        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($D11, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C11" s="74"/>
       <c r="D11" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9462,10 +9436,7 @@
       <c r="B12" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="82" t="str" cm="1">
-        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C12" s="82"/>
       <c r="D12" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9524,10 +9495,7 @@
       <c r="B13" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="74" t="str" cm="1">
-        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($D13, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C13" s="74"/>
       <c r="D13" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9586,10 +9554,7 @@
       <c r="B14" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="74" t="str" cm="1">
-        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($D14, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C14" s="74"/>
       <c r="D14" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9648,15 +9613,12 @@
       <c r="B15" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="82" t="str" cm="1">
-        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C15" s="82"/>
       <c r="D15" s="82" t="s">
         <v>1008</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F15" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9710,10 +9672,7 @@
       <c r="B16" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="74" t="str" cm="1">
-        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($D16, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C16" s="74"/>
       <c r="D16" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9772,10 +9731,7 @@
       <c r="B17" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="82" t="str" cm="1">
-        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C17" s="82"/>
       <c r="D17" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9834,10 +9790,7 @@
       <c r="B18" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="82" t="str" cm="1">
-        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C18" s="82"/>
       <c r="D18" s="82" t="s">
         <v>1008</v>
       </c>
@@ -9896,10 +9849,7 @@
       <c r="B19" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="74" t="str" cm="1">
-        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C19" s="74"/>
       <c r="D19" s="74" t="s">
         <v>1008</v>
       </c>
@@ -9958,10 +9908,7 @@
       <c r="B20" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="82" t="str" cm="1">
-        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C20" s="82"/>
       <c r="D20" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10020,10 +9967,7 @@
       <c r="B21" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="74" t="str" cm="1">
-        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C21" s="74"/>
       <c r="D21" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10082,10 +10026,7 @@
       <c r="B22" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="74" t="str" cm="1">
-        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C22" s="74"/>
       <c r="D22" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10144,10 +10085,7 @@
       <c r="B23" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="82" t="str" cm="1">
-        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($D23, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C23" s="82"/>
       <c r="D23" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10206,10 +10144,7 @@
       <c r="B24" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="82" t="str" cm="1">
-        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($D24, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C24" s="82"/>
       <c r="D24" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10268,10 +10203,7 @@
       <c r="B25" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="74" t="str" cm="1">
-        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C25" s="74"/>
       <c r="D25" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10330,10 +10262,7 @@
       <c r="B26" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="74" t="str" cm="1">
-        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C26" s="74"/>
       <c r="D26" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10392,10 +10321,7 @@
       <c r="B27" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="82" t="str" cm="1">
-        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($D27, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C27" s="82"/>
       <c r="D27" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10454,10 +10380,7 @@
       <c r="B28" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="82" t="str" cm="1">
-        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C28" s="82"/>
       <c r="D28" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10516,10 +10439,7 @@
       <c r="B29" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="74" t="str" cm="1">
-        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C29" s="74"/>
       <c r="D29" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10578,10 +10498,7 @@
       <c r="B30" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="82" t="str" cm="1">
-        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C30" s="82"/>
       <c r="D30" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10640,10 +10557,7 @@
       <c r="B31" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="82" t="str" cm="1">
-        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C31" s="82"/>
       <c r="D31" s="82" t="s">
         <v>1009</v>
       </c>
@@ -10702,10 +10616,7 @@
       <c r="B32" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="74" t="str" cm="1">
-        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C32" s="74"/>
       <c r="D32" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10764,10 +10675,7 @@
       <c r="B33" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="74" t="str" cm="1">
-        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C33" s="74"/>
       <c r="D33" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10823,18 +10731,20 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B34" s="102" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C34" s="102"/>
+        <v>23</v>
+      </c>
+      <c r="C34" s="102" t="s">
+        <v>1113</v>
+      </c>
       <c r="D34" s="102" t="s">
         <v>1009</v>
       </c>
       <c r="E34" s="102" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F34" s="102" t="str">
         <f t="shared" si="6"/>
-        <v>p-dtg-cdmlap-lb-rule?</v>
+        <v>p-dtg-cdmlap-lb-rule3000</v>
       </c>
       <c r="G34" s="102" t="str">
         <f t="shared" ref="G34:G62" si="8">SUBSTITUTE(E34, "hazr-", "")&amp;"-fe"</f>
@@ -10843,8 +10753,8 @@
       <c r="H34" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="102" t="s">
-        <v>1082</v>
+      <c r="I34" s="102">
+        <v>3000</v>
       </c>
       <c r="J34" s="102" t="b">
         <v>0</v>
@@ -10853,18 +10763,18 @@
         <f t="shared" ref="K34:K62" si="9">SUBSTITUTE(E34, "hazr-", "")&amp;"-bp"</f>
         <v>p-dtg-cdmlap-lb-bp</v>
       </c>
-      <c r="L34" s="102" t="s">
-        <v>1082</v>
+      <c r="L34" s="102">
+        <v>3000</v>
       </c>
       <c r="M34" s="102" t="str">
         <f t="shared" si="7"/>
-        <v>p-dtg-cdmlap-lb-pb?</v>
+        <v>p-dtg-cdmlap-lb-pb3000</v>
       </c>
       <c r="N34" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="O34" s="102" t="s">
-        <v>1082</v>
+      <c r="O34" s="102">
+        <v>3000</v>
       </c>
       <c r="P34" s="102">
         <v>4</v>
@@ -10884,10 +10794,7 @@
       <c r="B35" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="74" t="str" cm="1">
-        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C35" s="74"/>
       <c r="D35" s="74" t="s">
         <v>1009</v>
       </c>
@@ -10946,10 +10853,7 @@
       <c r="B36" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="74" t="str" cm="1">
-        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C36" s="74"/>
       <c r="D36" s="74" t="s">
         <v>1009</v>
       </c>
@@ -11008,15 +10912,12 @@
       <c r="B37" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="82" t="str" cm="1">
-        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($D37, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C37" s="82"/>
       <c r="D37" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F37" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11070,15 +10971,12 @@
       <c r="B38" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="82" t="str" cm="1">
-        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C38" s="82"/>
       <c r="D38" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F38" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11132,15 +11030,12 @@
       <c r="B39" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="82" t="str" cm="1">
-        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($D39, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C39" s="82"/>
       <c r="D39" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F39" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11194,15 +11089,12 @@
       <c r="B40" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="82" t="str" cm="1">
-        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($D40, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C40" s="82"/>
       <c r="D40" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F40" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11256,15 +11148,12 @@
       <c r="B41" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="82" t="str" cm="1">
-        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C41" s="82"/>
       <c r="D41" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F41" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11318,10 +11207,7 @@
       <c r="B42" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="74" t="str" cm="1">
-        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($D42, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C42" s="74"/>
       <c r="D42" s="74" t="s">
         <v>1009</v>
       </c>
@@ -11380,15 +11266,12 @@
       <c r="B43" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="82" t="str" cm="1">
-        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($D43, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C43" s="82"/>
       <c r="D43" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F43" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11442,10 +11325,7 @@
       <c r="B44" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="74" t="str" cm="1">
-        <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($D44, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C44" s="74"/>
       <c r="D44" s="74" t="s">
         <v>1009</v>
       </c>
@@ -11504,15 +11384,12 @@
       <c r="B45" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="82" t="str" cm="1">
-        <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($D45, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C45" s="82"/>
       <c r="D45" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F45" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11566,10 +11443,7 @@
       <c r="B46" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="74" t="str" cm="1">
-        <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($D46, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C46" s="74"/>
       <c r="D46" s="74" t="s">
         <v>1010</v>
       </c>
@@ -11628,15 +11502,12 @@
       <c r="B47" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="82" t="str" cm="1">
-        <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($D47, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C47" s="82"/>
       <c r="D47" s="82" t="s">
         <v>1010</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F47" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11690,10 +11561,7 @@
       <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="74" t="str" cm="1">
-        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C48" s="74"/>
       <c r="D48" s="74" t="s">
         <v>1011</v>
       </c>
@@ -11752,10 +11620,7 @@
       <c r="B49" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="74" t="str" cm="1">
-        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C49" s="74"/>
       <c r="D49" s="74" t="s">
         <v>1011</v>
       </c>
@@ -11814,10 +11679,7 @@
       <c r="B50" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="74" t="str" cm="1">
-        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C50" s="74"/>
       <c r="D50" s="74" t="s">
         <v>1011</v>
       </c>
@@ -11876,15 +11738,12 @@
       <c r="B51" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="82" t="str" cm="1">
-        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C51" s="82"/>
       <c r="D51" s="82" t="s">
         <v>1011</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F51" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11938,15 +11797,12 @@
       <c r="B52" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="82" t="str" cm="1">
-        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C52" s="82"/>
       <c r="D52" s="82" t="s">
         <v>1011</v>
       </c>
       <c r="E52" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F52" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11997,7 +11853,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C53" s="102"/>
       <c r="D53" s="102" t="s">
@@ -12018,7 +11874,7 @@
         <v>57</v>
       </c>
       <c r="I53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J53" s="102" t="b">
         <v>0</v>
@@ -12028,7 +11884,7 @@
         <v>p-cs-chtap-lb-bp</v>
       </c>
       <c r="L53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M53" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12038,7 +11894,7 @@
         <v>57</v>
       </c>
       <c r="O53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P53" s="102">
         <v>4</v>
@@ -12055,14 +11911,14 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C54" s="102"/>
       <c r="D54" s="102" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F54" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12076,7 +11932,7 @@
         <v>57</v>
       </c>
       <c r="I54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J54" s="102" t="b">
         <v>0</v>
@@ -12086,7 +11942,7 @@
         <v>p-cs-chtweb-lb-bp</v>
       </c>
       <c r="L54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M54" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12096,7 +11952,7 @@
         <v>57</v>
       </c>
       <c r="O54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P54" s="102">
         <v>4</v>
@@ -12113,7 +11969,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C55" s="102"/>
       <c r="D55" s="102" t="s">
@@ -12134,7 +11990,7 @@
         <v>57</v>
       </c>
       <c r="I55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J55" s="102" t="b">
         <v>0</v>
@@ -12144,7 +12000,7 @@
         <v>p-cs-chtintweb-lb-bp</v>
       </c>
       <c r="L55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M55" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12154,7 +12010,7 @@
         <v>57</v>
       </c>
       <c r="O55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P55" s="102">
         <v>4</v>
@@ -12171,14 +12027,14 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C56" s="102"/>
       <c r="D56" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F56" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12192,7 +12048,7 @@
         <v>57</v>
       </c>
       <c r="I56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J56" s="102" t="b">
         <v>0</v>
@@ -12202,7 +12058,7 @@
         <v>p-doip-web-lb-bp</v>
       </c>
       <c r="L56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M56" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12212,7 +12068,7 @@
         <v>57</v>
       </c>
       <c r="O56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P56" s="102">
         <v>4</v>
@@ -12229,7 +12085,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
@@ -12250,7 +12106,7 @@
         <v>57</v>
       </c>
       <c r="I57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J57" s="102" t="b">
         <v>0</v>
@@ -12260,7 +12116,7 @@
         <v>p-doip-ap-lb-bp</v>
       </c>
       <c r="L57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M57" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12270,7 +12126,7 @@
         <v>57</v>
       </c>
       <c r="O57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P57" s="102">
         <v>4</v>
@@ -12287,14 +12143,14 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F58" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12308,7 +12164,7 @@
         <v>57</v>
       </c>
       <c r="I58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J58" s="102" t="b">
         <v>0</v>
@@ -12318,7 +12174,7 @@
         <v>p-doip-adm-lb-bp</v>
       </c>
       <c r="L58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M58" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12328,7 +12184,7 @@
         <v>57</v>
       </c>
       <c r="O58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P58" s="102">
         <v>4</v>
@@ -12348,10 +12204,7 @@
       <c r="B59" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C59" s="74" t="str" cm="1">
-        <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C59" s="74"/>
       <c r="D59" s="74" t="s">
         <v>1010</v>
       </c>
@@ -12410,10 +12263,7 @@
       <c r="B60" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="74" t="str" cm="1">
-        <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C60" s="74"/>
       <c r="D60" s="74" t="s">
         <v>1010</v>
       </c>
@@ -12472,10 +12322,7 @@
       <c r="B61" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="82" t="str" cm="1">
-        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C61" s="82"/>
       <c r="D61" s="82" t="s">
         <v>1010</v>
       </c>
@@ -12534,10 +12381,7 @@
       <c r="B62" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="74" t="str" cm="1">
-        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C62" s="74"/>
       <c r="D62" s="74" t="s">
         <v>1010</v>
       </c>
@@ -12988,7 +12832,7 @@
         <v>640</v>
       </c>
       <c r="N2" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O2" s="74" t="str">
         <f t="shared" ref="O2:O6" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -13074,7 +12918,7 @@
         <v>640</v>
       </c>
       <c r="N3" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O3" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13160,7 +13004,7 @@
         <v>640</v>
       </c>
       <c r="N4" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O4" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13246,7 +13090,7 @@
         <v>640</v>
       </c>
       <c r="N5" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O5" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13314,7 +13158,7 @@
         <v>499</v>
       </c>
       <c r="H6" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I6" s="80">
         <v>2</v>
@@ -13332,7 +13176,7 @@
         <v>640</v>
       </c>
       <c r="N6" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O6" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13400,7 +13244,7 @@
         <v>500</v>
       </c>
       <c r="H7" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I7" s="80">
         <v>2</v>
@@ -13418,7 +13262,7 @@
         <v>640</v>
       </c>
       <c r="N7" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O7" s="74" t="str">
         <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
@@ -13504,7 +13348,7 @@
         <v>640</v>
       </c>
       <c r="N8" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O8" s="74" t="str">
         <f t="shared" ref="O8:O39" si="2">SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
@@ -13590,7 +13434,7 @@
         <v>640</v>
       </c>
       <c r="N9" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O9" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13676,7 +13520,7 @@
         <v>640</v>
       </c>
       <c r="N10" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O10" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13762,7 +13606,7 @@
         <v>640</v>
       </c>
       <c r="N11" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O11" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13848,7 +13692,7 @@
         <v>640</v>
       </c>
       <c r="N12" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O12" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13934,7 +13778,7 @@
         <v>640</v>
       </c>
       <c r="N13" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O13" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14020,7 +13864,7 @@
         <v>640</v>
       </c>
       <c r="N14" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O14" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14106,7 +13950,7 @@
         <v>640</v>
       </c>
       <c r="N15" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O15" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14192,7 +14036,7 @@
         <v>640</v>
       </c>
       <c r="N16" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O16" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14260,7 +14104,7 @@
         <v>510</v>
       </c>
       <c r="H17" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I17" s="80">
         <v>2</v>
@@ -14278,7 +14122,7 @@
         <v>640</v>
       </c>
       <c r="N17" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O17" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14346,7 +14190,7 @@
         <v>511</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I18" s="80">
         <v>2</v>
@@ -14364,7 +14208,7 @@
         <v>640</v>
       </c>
       <c r="N18" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O18" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14432,7 +14276,7 @@
         <v>512</v>
       </c>
       <c r="H19" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I19" s="80">
         <v>2</v>
@@ -14450,7 +14294,7 @@
         <v>640</v>
       </c>
       <c r="N19" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O19" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14518,7 +14362,7 @@
         <v>513</v>
       </c>
       <c r="H20" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I20" s="80">
         <v>2</v>
@@ -14536,7 +14380,7 @@
         <v>640</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O20" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14622,7 +14466,7 @@
         <v>640</v>
       </c>
       <c r="N21" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O21" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14708,7 +14552,7 @@
         <v>640</v>
       </c>
       <c r="N22" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O22" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14794,7 +14638,7 @@
         <v>640</v>
       </c>
       <c r="N23" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O23" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14880,7 +14724,7 @@
         <v>640</v>
       </c>
       <c r="N24" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O24" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14966,7 +14810,7 @@
         <v>640</v>
       </c>
       <c r="N25" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O25" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15052,7 +14896,7 @@
         <v>640</v>
       </c>
       <c r="N26" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O26" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15138,7 +14982,7 @@
         <v>640</v>
       </c>
       <c r="N27" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O27" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15224,7 +15068,7 @@
         <v>640</v>
       </c>
       <c r="N28" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O28" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15310,7 +15154,7 @@
         <v>640</v>
       </c>
       <c r="N29" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O29" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15396,7 +15240,7 @@
         <v>640</v>
       </c>
       <c r="N30" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O30" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15482,7 +15326,7 @@
         <v>640</v>
       </c>
       <c r="N31" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O31" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15568,7 +15412,7 @@
         <v>640</v>
       </c>
       <c r="N32" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O32" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15654,7 +15498,7 @@
         <v>640</v>
       </c>
       <c r="N33" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O33" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15740,7 +15584,7 @@
         <v>640</v>
       </c>
       <c r="N34" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O34" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15826,7 +15670,7 @@
         <v>641</v>
       </c>
       <c r="N35" s="98" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="O35" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15912,7 +15756,7 @@
         <v>640</v>
       </c>
       <c r="N36" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O36" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15998,7 +15842,7 @@
         <v>640</v>
       </c>
       <c r="N37" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O37" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16084,7 +15928,7 @@
         <v>640</v>
       </c>
       <c r="N38" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O38" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16170,7 +16014,7 @@
         <v>640</v>
       </c>
       <c r="N39" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O39" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16256,7 +16100,7 @@
         <v>640</v>
       </c>
       <c r="N40" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O40" s="74" t="str">
         <f t="shared" ref="O40:O64" si="3">SUBSTITUTE(F40,"hazr-","")&amp;"-osdisk"</f>
@@ -16342,7 +16186,7 @@
         <v>640</v>
       </c>
       <c r="N41" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O41" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16428,7 +16272,7 @@
         <v>640</v>
       </c>
       <c r="N42" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O42" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16514,7 +16358,7 @@
         <v>640</v>
       </c>
       <c r="N43" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O43" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16600,7 +16444,7 @@
         <v>640</v>
       </c>
       <c r="N44" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O44" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16686,7 +16530,7 @@
         <v>640</v>
       </c>
       <c r="N45" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O45" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16772,7 +16616,7 @@
         <v>640</v>
       </c>
       <c r="N46" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O46" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16858,7 +16702,7 @@
         <v>640</v>
       </c>
       <c r="N47" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O47" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16944,7 +16788,7 @@
         <v>640</v>
       </c>
       <c r="N48" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O48" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17030,7 +16874,7 @@
         <v>640</v>
       </c>
       <c r="N49" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O49" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17116,7 +16960,7 @@
         <v>640</v>
       </c>
       <c r="N50" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O50" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17202,7 +17046,7 @@
         <v>640</v>
       </c>
       <c r="N51" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O51" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17288,7 +17132,7 @@
         <v>640</v>
       </c>
       <c r="N52" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O52" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17374,7 +17218,7 @@
         <v>640</v>
       </c>
       <c r="N53" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O53" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17460,7 +17304,7 @@
         <v>640</v>
       </c>
       <c r="N54" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O54" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17546,7 +17390,7 @@
         <v>640</v>
       </c>
       <c r="N55" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O55" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17632,7 +17476,7 @@
         <v>640</v>
       </c>
       <c r="N56" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O56" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17718,7 +17562,7 @@
         <v>640</v>
       </c>
       <c r="N57" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O57" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17804,7 +17648,7 @@
         <v>640</v>
       </c>
       <c r="N58" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O58" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17890,7 +17734,7 @@
         <v>640</v>
       </c>
       <c r="N59" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O59" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17976,7 +17820,7 @@
         <v>640</v>
       </c>
       <c r="N60" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O60" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18062,7 +17906,7 @@
         <v>640</v>
       </c>
       <c r="N61" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O61" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18148,7 +17992,7 @@
         <v>640</v>
       </c>
       <c r="N62" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O62" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18234,7 +18078,7 @@
         <v>640</v>
       </c>
       <c r="N63" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O63" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18320,7 +18164,7 @@
         <v>640</v>
       </c>
       <c r="N64" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O64" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18406,7 +18250,7 @@
         <v>640</v>
       </c>
       <c r="N65" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O65" s="74" t="str">
         <f t="shared" ref="O65:O70" si="4">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
@@ -18492,7 +18336,7 @@
         <v>640</v>
       </c>
       <c r="N66" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O66" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18578,7 +18422,7 @@
         <v>640</v>
       </c>
       <c r="N67" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O67" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18664,7 +18508,7 @@
         <v>640</v>
       </c>
       <c r="N68" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O68" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18750,7 +18594,7 @@
         <v>640</v>
       </c>
       <c r="N69" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O69" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18836,7 +18680,7 @@
         <v>640</v>
       </c>
       <c r="N70" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O70" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18922,7 +18766,7 @@
         <v>640</v>
       </c>
       <c r="N71" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O71" s="74" t="str">
         <f t="shared" ref="O71:O102" si="6">SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
@@ -19008,7 +18852,7 @@
         <v>640</v>
       </c>
       <c r="N72" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O72" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19094,7 +18938,7 @@
         <v>640</v>
       </c>
       <c r="N73" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O73" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19180,7 +19024,7 @@
         <v>640</v>
       </c>
       <c r="N74" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O74" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19266,7 +19110,7 @@
         <v>640</v>
       </c>
       <c r="N75" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O75" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19352,7 +19196,7 @@
         <v>640</v>
       </c>
       <c r="N76" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O76" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19438,7 +19282,7 @@
         <v>640</v>
       </c>
       <c r="N77" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O77" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19524,7 +19368,7 @@
         <v>640</v>
       </c>
       <c r="N78" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O78" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19610,7 +19454,7 @@
         <v>640</v>
       </c>
       <c r="N79" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O79" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19696,7 +19540,7 @@
         <v>640</v>
       </c>
       <c r="N80" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O80" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19782,7 +19626,7 @@
         <v>640</v>
       </c>
       <c r="N81" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O81" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19868,7 +19712,7 @@
         <v>640</v>
       </c>
       <c r="N82" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O82" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19954,7 +19798,7 @@
         <v>640</v>
       </c>
       <c r="N83" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O83" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20040,7 +19884,7 @@
         <v>640</v>
       </c>
       <c r="N84" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O84" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20126,7 +19970,7 @@
         <v>640</v>
       </c>
       <c r="N85" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O85" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20212,7 +20056,7 @@
         <v>640</v>
       </c>
       <c r="N86" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O86" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20298,7 +20142,7 @@
         <v>640</v>
       </c>
       <c r="N87" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O87" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20384,7 +20228,7 @@
         <v>640</v>
       </c>
       <c r="N88" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O88" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20449,7 +20293,7 @@
         <v>438</v>
       </c>
       <c r="G89" s="80" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H89" s="80" t="s">
         <v>638</v>
@@ -20470,7 +20314,7 @@
         <v>640</v>
       </c>
       <c r="N89" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O89" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20556,7 +20400,7 @@
         <v>640</v>
       </c>
       <c r="N90" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O90" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20642,7 +20486,7 @@
         <v>640</v>
       </c>
       <c r="N91" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O91" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20728,7 +20572,7 @@
         <v>640</v>
       </c>
       <c r="N92" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O92" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20814,7 +20658,7 @@
         <v>640</v>
       </c>
       <c r="N93" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O93" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20900,7 +20744,7 @@
         <v>640</v>
       </c>
       <c r="N94" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O94" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20986,7 +20830,7 @@
         <v>640</v>
       </c>
       <c r="N95" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O95" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21072,7 +20916,7 @@
         <v>640</v>
       </c>
       <c r="N96" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O96" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21158,7 +21002,7 @@
         <v>640</v>
       </c>
       <c r="N97" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O97" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21244,7 +21088,7 @@
         <v>640</v>
       </c>
       <c r="N98" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O98" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21330,7 +21174,7 @@
         <v>640</v>
       </c>
       <c r="N99" s="98" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="O99" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21416,7 +21260,7 @@
         <v>640</v>
       </c>
       <c r="N100" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O100" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21502,7 +21346,7 @@
         <v>640</v>
       </c>
       <c r="N101" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O101" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21588,7 +21432,7 @@
         <v>640</v>
       </c>
       <c r="N102" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O102" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21674,7 +21518,7 @@
         <v>640</v>
       </c>
       <c r="N103" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O103" s="74" t="str">
         <f t="shared" ref="O103:O134" si="8">SUBSTITUTE(F103,"hazr-","")&amp;"-osdisk"</f>
@@ -21760,7 +21604,7 @@
         <v>640</v>
       </c>
       <c r="N104" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O104" s="74" t="str">
         <f t="shared" si="8"/>
@@ -21846,7 +21690,7 @@
         <v>640</v>
       </c>
       <c r="N105" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O105" s="74" t="str">
         <f t="shared" si="8"/>
@@ -21932,7 +21776,7 @@
         <v>640</v>
       </c>
       <c r="N106" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O106" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22018,7 +21862,7 @@
         <v>640</v>
       </c>
       <c r="N107" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O107" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22104,7 +21948,7 @@
         <v>640</v>
       </c>
       <c r="N108" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O108" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22190,7 +22034,7 @@
         <v>640</v>
       </c>
       <c r="N109" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O109" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22276,7 +22120,7 @@
         <v>640</v>
       </c>
       <c r="N110" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O110" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22362,7 +22206,7 @@
         <v>640</v>
       </c>
       <c r="N111" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O111" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22448,7 +22292,7 @@
         <v>640</v>
       </c>
       <c r="N112" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O112" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22534,7 +22378,7 @@
         <v>640</v>
       </c>
       <c r="N113" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O113" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22620,7 +22464,7 @@
         <v>640</v>
       </c>
       <c r="N114" s="98" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="O114" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22671,7 +22515,7 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B115" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C115" s="102" t="str" cm="1">
         <f t="array" ref="C115">UPPER(INDEX(_xlfn.TEXTSPLIT($D115, "-"), 3))</f>
@@ -22708,7 +22552,7 @@
         <v>640</v>
       </c>
       <c r="N115" s="105" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="O115" s="102" t="str">
         <f t="shared" si="8"/>
@@ -22759,7 +22603,7 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B116" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C116" s="102" t="str" cm="1">
         <f t="array" ref="C116">UPPER(INDEX(_xlfn.TEXTSPLIT($D116, "-"), 3))</f>
@@ -22796,7 +22640,7 @@
         <v>640</v>
       </c>
       <c r="N116" s="105" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O116" s="102" t="str">
         <f t="shared" si="8"/>
@@ -22864,7 +22708,7 @@
         <v>609</v>
       </c>
       <c r="H117" s="80" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I117" s="80">
         <v>2</v>
@@ -22882,7 +22726,7 @@
         <v>640</v>
       </c>
       <c r="N117" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O117" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22968,7 +22812,7 @@
         <v>640</v>
       </c>
       <c r="N118" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O118" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23019,7 +22863,7 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B119" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C119" s="102" t="str" cm="1">
         <f t="array" ref="C119">UPPER(INDEX(_xlfn.TEXTSPLIT($D119, "-"), 3))</f>
@@ -23056,7 +22900,7 @@
         <v>640</v>
       </c>
       <c r="N119" s="105" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O119" s="102" t="str">
         <f t="shared" si="8"/>
@@ -23108,7 +22952,7 @@
     <row r="120" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C120" s="74"/>
       <c r="D120" s="80" t="s">
@@ -23142,7 +22986,7 @@
         <v>640</v>
       </c>
       <c r="N120" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O120" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23194,7 +23038,7 @@
     <row r="121" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C121" s="74"/>
       <c r="D121" s="80" t="s">
@@ -23228,7 +23072,7 @@
         <v>640</v>
       </c>
       <c r="N121" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O121" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23280,7 +23124,7 @@
     <row r="122" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C122" s="74"/>
       <c r="D122" s="80" t="s">
@@ -23314,7 +23158,7 @@
         <v>640</v>
       </c>
       <c r="N122" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O122" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23400,7 +23244,7 @@
         <v>640</v>
       </c>
       <c r="N123" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O123" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23451,7 +23295,7 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B124" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C124" s="102"/>
       <c r="D124" s="102" t="s">
@@ -23464,10 +23308,10 @@
         <v>470</v>
       </c>
       <c r="G124" s="102" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H124" s="102" t="s">
         <v>1094</v>
-      </c>
-      <c r="H124" s="102" t="s">
-        <v>1095</v>
       </c>
       <c r="I124" s="102">
         <v>2</v>
@@ -23482,7 +23326,7 @@
         <v>179</v>
       </c>
       <c r="M124" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N124" s="102"/>
       <c r="O124" s="102" t="str">
@@ -23534,7 +23378,7 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B125" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C125" s="102"/>
       <c r="D125" s="102" t="s">
@@ -23547,10 +23391,10 @@
         <v>471</v>
       </c>
       <c r="G125" s="102" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H125" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I125" s="102">
         <v>2</v>
@@ -23565,7 +23409,7 @@
         <v>179</v>
       </c>
       <c r="M125" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N125" s="102"/>
       <c r="O125" s="102" t="str">
@@ -23652,7 +23496,7 @@
         <v>640</v>
       </c>
       <c r="N126" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O126" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23738,7 +23582,7 @@
         <v>640</v>
       </c>
       <c r="N127" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O127" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23824,7 +23668,7 @@
         <v>640</v>
       </c>
       <c r="N128" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O128" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23910,7 +23754,7 @@
         <v>640</v>
       </c>
       <c r="N129" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O129" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23996,7 +23840,7 @@
         <v>640</v>
       </c>
       <c r="N130" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O130" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24082,7 +23926,7 @@
         <v>640</v>
       </c>
       <c r="N131" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O131" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24133,7 +23977,7 @@
     </row>
     <row r="132" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B132" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C132" s="102" t="str" cm="1">
         <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
@@ -24149,10 +23993,10 @@
         <v>478</v>
       </c>
       <c r="G132" s="102" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H132" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I132" s="102">
         <v>2</v>
@@ -24167,10 +24011,10 @@
         <v>179</v>
       </c>
       <c r="M132" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N132" s="105" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O132" s="102" t="str">
         <f t="shared" si="8"/>
@@ -24221,7 +24065,7 @@
     </row>
     <row r="133" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B133" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C133" s="102" t="str" cm="1">
         <f t="array" ref="C133">UPPER(INDEX(_xlfn.TEXTSPLIT($D133, "-"), 3))</f>
@@ -24237,10 +24081,10 @@
         <v>479</v>
       </c>
       <c r="G133" s="102" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H133" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I133" s="102">
         <v>2</v>
@@ -24255,10 +24099,10 @@
         <v>179</v>
       </c>
       <c r="M133" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N133" s="105" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O133" s="102" t="str">
         <f t="shared" si="8"/>
@@ -24309,7 +24153,7 @@
     </row>
     <row r="134" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B134" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C134" s="102" t="str" cm="1">
         <f t="array" ref="C134">UPPER(INDEX(_xlfn.TEXTSPLIT($D134, "-"), 3))</f>
@@ -24325,10 +24169,10 @@
         <v>480</v>
       </c>
       <c r="G134" s="102" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H134" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I134" s="102">
         <v>2</v>
@@ -24343,10 +24187,10 @@
         <v>179</v>
       </c>
       <c r="M134" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N134" s="115" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O134" s="102" t="str">
         <f t="shared" si="8"/>
@@ -24397,7 +24241,7 @@
     </row>
     <row r="135" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B135" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C135" s="102" t="str" cm="1">
         <f t="array" ref="C135">UPPER(INDEX(_xlfn.TEXTSPLIT($D135, "-"), 3))</f>
@@ -24413,10 +24257,10 @@
         <v>481</v>
       </c>
       <c r="G135" s="102" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H135" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I135" s="102">
         <v>2</v>
@@ -24431,10 +24275,10 @@
         <v>179</v>
       </c>
       <c r="M135" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N135" s="115" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O135" s="102" t="str">
         <f t="shared" ref="O135:O146" si="10">SUBSTITUTE(F135,"hazr-","")&amp;"-osdisk"</f>
@@ -24485,7 +24329,7 @@
     </row>
     <row r="136" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B136" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C136" s="102" t="str" cm="1">
         <f t="array" ref="C136">UPPER(INDEX(_xlfn.TEXTSPLIT($D136, "-"), 3))</f>
@@ -24501,10 +24345,10 @@
         <v>482</v>
       </c>
       <c r="G136" s="102" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H136" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I136" s="102">
         <v>2</v>
@@ -24519,10 +24363,10 @@
         <v>179</v>
       </c>
       <c r="M136" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N136" s="115" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O136" s="102" t="str">
         <f t="shared" si="10"/>
@@ -24573,7 +24417,7 @@
     </row>
     <row r="137" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B137" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C137" s="102" t="str" cm="1">
         <f t="array" ref="C137">UPPER(INDEX(_xlfn.TEXTSPLIT($D137, "-"), 3))</f>
@@ -24589,10 +24433,10 @@
         <v>483</v>
       </c>
       <c r="G137" s="102" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H137" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I137" s="102">
         <v>2</v>
@@ -24607,10 +24451,10 @@
         <v>179</v>
       </c>
       <c r="M137" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N137" s="115" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O137" s="102" t="str">
         <f t="shared" si="10"/>
@@ -24696,7 +24540,7 @@
         <v>640</v>
       </c>
       <c r="N138" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O138" s="74" t="str">
         <f t="shared" si="10"/>
@@ -24782,7 +24626,7 @@
         <v>640</v>
       </c>
       <c r="N139" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O139" s="74" t="str">
         <f t="shared" si="10"/>
@@ -24868,7 +24712,7 @@
         <v>640</v>
       </c>
       <c r="N140" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O140" s="74" t="str">
         <f t="shared" si="10"/>
@@ -24954,7 +24798,7 @@
         <v>640</v>
       </c>
       <c r="N141" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O141" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25040,7 +24884,7 @@
         <v>640</v>
       </c>
       <c r="N142" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O142" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25126,7 +24970,7 @@
         <v>640</v>
       </c>
       <c r="N143" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O143" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25212,7 +25056,7 @@
         <v>640</v>
       </c>
       <c r="N144" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O144" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25264,7 +25108,7 @@
     <row r="145" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C145" s="74"/>
       <c r="D145" s="80" t="s">
@@ -25277,7 +25121,7 @@
         <v>491</v>
       </c>
       <c r="G145" s="80" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H145" s="80" t="s">
         <v>634</v>
@@ -25298,7 +25142,7 @@
         <v>640</v>
       </c>
       <c r="N145" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O145" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25330,7 +25174,7 @@
         <v>225</v>
       </c>
       <c r="Z145" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AA145" s="74" t="b">
         <v>1</v>
@@ -25350,7 +25194,7 @@
     <row r="146" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C146" s="74"/>
       <c r="D146" s="80" t="s">
@@ -25363,7 +25207,7 @@
         <v>492</v>
       </c>
       <c r="G146" s="80" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H146" s="80" t="s">
         <v>630</v>
@@ -25384,7 +25228,7 @@
         <v>640</v>
       </c>
       <c r="N146" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O146" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25416,7 +25260,7 @@
         <v>225</v>
       </c>
       <c r="Z146" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AA146" s="74" t="b">
         <v>1</v>
@@ -32320,7 +32164,7 @@
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" s="99"/>
       <c r="B130" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C130" s="73" t="str" cm="1">
         <f t="array" ref="C130">UPPER(INDEX(_xlfn.TEXTSPLIT($D130, "-"), 3))</f>
@@ -32373,7 +32217,7 @@
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="99"/>
       <c r="B131" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C131" s="74" t="str" cm="1">
         <f t="array" ref="C131">UPPER(INDEX(_xlfn.TEXTSPLIT($D131, "-"), 3))</f>
@@ -32426,7 +32270,7 @@
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="99"/>
       <c r="B132" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C132" s="73" t="str" cm="1">
         <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
@@ -33806,7 +33650,7 @@
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="99"/>
       <c r="B158" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C158" s="74" t="str" cm="1">
         <f t="array" ref="C158">UPPER(INDEX(_xlfn.TEXTSPLIT($D158, "-"), 3))</f>
@@ -33859,7 +33703,7 @@
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="99"/>
       <c r="B159" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C159" s="73" t="str" cm="1">
         <f t="array" ref="C159">UPPER(INDEX(_xlfn.TEXTSPLIT($D159, "-"), 3))</f>
@@ -36756,7 +36600,7 @@
         <v>241</v>
       </c>
       <c r="H71" s="74" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I71" s="74" t="s">
         <v>420</v>
@@ -36796,7 +36640,7 @@
         <v>241</v>
       </c>
       <c r="H72" s="73" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I72" s="73" t="s">
         <v>421</v>
@@ -36836,7 +36680,7 @@
         <v>241</v>
       </c>
       <c r="H73" s="74" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I73" s="74" t="s">
         <v>422</v>
@@ -36876,7 +36720,7 @@
         <v>241</v>
       </c>
       <c r="H74" s="73" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I74" s="73" t="s">
         <v>423</v>
@@ -38693,7 +38537,7 @@
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C120" s="78" t="str" cm="1">
         <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($E120, "-"), 2))</f>
@@ -38713,7 +38557,7 @@
         <v>241</v>
       </c>
       <c r="H120" s="73" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I120" s="73" t="s">
         <v>233</v>
@@ -38733,7 +38577,7 @@
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C121" s="80" t="str" cm="1">
         <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($E121, "-"), 2))</f>
@@ -38753,7 +38597,7 @@
         <v>241</v>
       </c>
       <c r="H121" s="74" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I121" s="74" t="s">
         <v>232</v>
@@ -38773,7 +38617,7 @@
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C122" s="78" t="str" cm="1">
         <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($E122, "-"), 2))</f>
@@ -38793,7 +38637,7 @@
         <v>241</v>
       </c>
       <c r="H122" s="73" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I122" s="73" t="s">
         <v>236</v>
@@ -39685,10 +39529,10 @@
     <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="80" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C145" s="80" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D145" s="80" t="s">
         <v>234</v>
@@ -39704,7 +39548,7 @@
         <v>225</v>
       </c>
       <c r="H145" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I145" s="74" t="s">
         <v>491</v>
@@ -39724,10 +39568,10 @@
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="78" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C146" s="78" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D146" s="78" t="s">
         <v>234</v>
@@ -39743,7 +39587,7 @@
         <v>225</v>
       </c>
       <c r="H146" s="73" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I146" s="73" t="s">
         <v>492</v>
@@ -41806,7 +41650,7 @@
         <v>332</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>222</v>
@@ -42437,7 +42281,7 @@
         <v>332</v>
       </c>
       <c r="H29" s="82" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I29" s="82" t="s">
         <v>222</v>
@@ -45133,10 +44977,7 @@
       <c r="B2" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="82" t="str" cm="1">
-        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C2" s="82"/>
       <c r="D2" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45166,10 +45007,7 @@
       <c r="B3" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="74" t="str" cm="1">
-        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C3" s="74"/>
       <c r="D3" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45199,10 +45037,7 @@
       <c r="B4" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="82" t="str" cm="1">
-        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($D4, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C4" s="82"/>
       <c r="D4" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45232,10 +45067,7 @@
       <c r="B5" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="74" t="str" cm="1">
-        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C5" s="74"/>
       <c r="D5" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45265,10 +45097,7 @@
       <c r="B6" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="74" t="str" cm="1">
-        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C6" s="74"/>
       <c r="D6" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45298,10 +45127,7 @@
       <c r="B7" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="74" t="str" cm="1">
-        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C7" s="74"/>
       <c r="D7" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45331,10 +45157,7 @@
       <c r="B8" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="82" t="str" cm="1">
-        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C8" s="82"/>
       <c r="D8" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45364,10 +45187,7 @@
       <c r="B9" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="74" t="str" cm="1">
-        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C9" s="74"/>
       <c r="D9" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45397,10 +45217,7 @@
       <c r="B10" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="82" t="str" cm="1">
-        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C10" s="82"/>
       <c r="D10" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45430,10 +45247,7 @@
       <c r="B11" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="74" t="str" cm="1">
-        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($D11, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C11" s="74"/>
       <c r="D11" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45463,10 +45277,7 @@
       <c r="B12" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="82" t="str" cm="1">
-        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C12" s="82"/>
       <c r="D12" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45496,10 +45307,7 @@
       <c r="B13" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="74" t="str" cm="1">
-        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($D13, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C13" s="74"/>
       <c r="D13" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45529,10 +45337,7 @@
       <c r="B14" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="74" t="str" cm="1">
-        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($D14, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C14" s="74"/>
       <c r="D14" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45562,15 +45367,12 @@
       <c r="B15" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="82" t="str" cm="1">
-        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C15" s="82"/>
       <c r="D15" s="82" t="s">
         <v>1008</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F15" s="51" t="str">
         <f t="shared" si="0"/>
@@ -45595,10 +45397,7 @@
       <c r="B16" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="74" t="str" cm="1">
-        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($D16, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C16" s="74"/>
       <c r="D16" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45628,10 +45427,7 @@
       <c r="B17" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="82" t="str" cm="1">
-        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C17" s="82"/>
       <c r="D17" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45661,10 +45457,7 @@
       <c r="B18" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="82" t="str" cm="1">
-        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C18" s="82"/>
       <c r="D18" s="82" t="s">
         <v>1008</v>
       </c>
@@ -45694,10 +45487,7 @@
       <c r="B19" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="74" t="str" cm="1">
-        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C19" s="74"/>
       <c r="D19" s="74" t="s">
         <v>1008</v>
       </c>
@@ -45727,10 +45517,7 @@
       <c r="B20" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="82" t="str" cm="1">
-        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C20" s="82"/>
       <c r="D20" s="82" t="s">
         <v>1009</v>
       </c>
@@ -45760,10 +45547,7 @@
       <c r="B21" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="74" t="str" cm="1">
-        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C21" s="74"/>
       <c r="D21" s="74" t="s">
         <v>1009</v>
       </c>
@@ -45793,10 +45577,7 @@
       <c r="B22" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="74" t="str" cm="1">
-        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C22" s="74"/>
       <c r="D22" s="74" t="s">
         <v>1009</v>
       </c>
@@ -45826,10 +45607,7 @@
       <c r="B23" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="82" t="str" cm="1">
-        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($D23, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C23" s="82"/>
       <c r="D23" s="82" t="s">
         <v>1009</v>
       </c>
@@ -45859,10 +45637,7 @@
       <c r="B24" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="82" t="str" cm="1">
-        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($D24, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C24" s="82"/>
       <c r="D24" s="82" t="s">
         <v>1009</v>
       </c>
@@ -45892,10 +45667,7 @@
       <c r="B25" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="74" t="str" cm="1">
-        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C25" s="74"/>
       <c r="D25" s="74" t="s">
         <v>1009</v>
       </c>
@@ -45925,10 +45697,7 @@
       <c r="B26" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="74" t="str" cm="1">
-        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C26" s="74"/>
       <c r="D26" s="74" t="s">
         <v>1009</v>
       </c>
@@ -45958,10 +45727,7 @@
       <c r="B27" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="82" t="str" cm="1">
-        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($D27, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C27" s="82"/>
       <c r="D27" s="82" t="s">
         <v>1009</v>
       </c>
@@ -45991,10 +45757,7 @@
       <c r="B28" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="82" t="str" cm="1">
-        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C28" s="82"/>
       <c r="D28" s="82" t="s">
         <v>1009</v>
       </c>
@@ -46024,10 +45787,7 @@
       <c r="B29" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="74" t="str" cm="1">
-        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C29" s="74"/>
       <c r="D29" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46057,10 +45817,7 @@
       <c r="B30" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="82" t="str" cm="1">
-        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C30" s="82"/>
       <c r="D30" s="82" t="s">
         <v>1009</v>
       </c>
@@ -46090,10 +45847,7 @@
       <c r="B31" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="82" t="str" cm="1">
-        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C31" s="82"/>
       <c r="D31" s="82" t="s">
         <v>1009</v>
       </c>
@@ -46123,10 +45877,7 @@
       <c r="B32" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="74" t="str" cm="1">
-        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C32" s="74"/>
       <c r="D32" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46156,10 +45907,7 @@
       <c r="B33" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="74" t="str" cm="1">
-        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C33" s="74"/>
       <c r="D33" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46186,24 +45934,26 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B34" s="102" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C34" s="102"/>
+        <v>23</v>
+      </c>
+      <c r="C34" s="102" t="s">
+        <v>1112</v>
+      </c>
       <c r="D34" s="102" t="s">
         <v>1009</v>
       </c>
       <c r="E34" s="102" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F34" s="107" t="str">
         <f t="shared" si="0"/>
-        <v>p-dtg-cdmlap-lb-pb?</v>
+        <v>p-dtg-cdmlap-lb-pb3000</v>
       </c>
       <c r="G34" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="102" t="s">
-        <v>1082</v>
+      <c r="H34" s="102">
+        <v>3000</v>
       </c>
       <c r="I34" s="102"/>
       <c r="J34" s="102">
@@ -46218,10 +45968,7 @@
       <c r="B35" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="74" t="str" cm="1">
-        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C35" s="74"/>
       <c r="D35" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46251,10 +45998,7 @@
       <c r="B36" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="74" t="str" cm="1">
-        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C36" s="74"/>
       <c r="D36" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46284,15 +46028,12 @@
       <c r="B37" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="82" t="str" cm="1">
-        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($D37, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C37" s="82"/>
       <c r="D37" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F37" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46317,15 +46058,12 @@
       <c r="B38" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="82" t="str" cm="1">
-        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C38" s="82"/>
       <c r="D38" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F38" s="51" t="str">
         <f t="shared" ref="F38:F41" si="9">SUBSTITUTE(E38, "hazr-", "")&amp;"-pb"&amp;H38</f>
@@ -46350,15 +46088,12 @@
       <c r="B39" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="82" t="str" cm="1">
-        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($D39, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C39" s="82"/>
       <c r="D39" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F39" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46383,15 +46118,12 @@
       <c r="B40" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="82" t="str" cm="1">
-        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($D40, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C40" s="82"/>
       <c r="D40" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F40" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46416,15 +46148,12 @@
       <c r="B41" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="82" t="str" cm="1">
-        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C41" s="82"/>
       <c r="D41" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F41" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46449,10 +46178,7 @@
       <c r="B42" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="74" t="str" cm="1">
-        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($D42, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C42" s="74"/>
       <c r="D42" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46482,15 +46208,12 @@
       <c r="B43" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="82" t="str" cm="1">
-        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($D43, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C43" s="82"/>
       <c r="D43" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F43" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46515,10 +46238,7 @@
       <c r="B44" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="74" t="str" cm="1">
-        <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($D44, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C44" s="74"/>
       <c r="D44" s="74" t="s">
         <v>1009</v>
       </c>
@@ -46548,15 +46268,12 @@
       <c r="B45" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="82" t="str" cm="1">
-        <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($D45, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C45" s="82"/>
       <c r="D45" s="82" t="s">
         <v>1009</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F45" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46581,10 +46298,7 @@
       <c r="B46" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="74" t="str" cm="1">
-        <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($D46, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C46" s="74"/>
       <c r="D46" s="74" t="s">
         <v>1010</v>
       </c>
@@ -46614,15 +46328,12 @@
       <c r="B47" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="82" t="str" cm="1">
-        <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($D47, "-"), 3))</f>
-        <v>BDP</v>
-      </c>
+      <c r="C47" s="82"/>
       <c r="D47" s="82" t="s">
         <v>1010</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F47" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46647,10 +46358,7 @@
       <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="74" t="str" cm="1">
-        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C48" s="74"/>
       <c r="D48" s="74" t="s">
         <v>1011</v>
       </c>
@@ -46680,10 +46388,7 @@
       <c r="B49" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="74" t="str" cm="1">
-        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C49" s="74"/>
       <c r="D49" s="74" t="s">
         <v>1011</v>
       </c>
@@ -46713,10 +46418,7 @@
       <c r="B50" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="74" t="str" cm="1">
-        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C50" s="74"/>
       <c r="D50" s="74" t="s">
         <v>1011</v>
       </c>
@@ -46746,15 +46448,12 @@
       <c r="B51" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="82" t="str" cm="1">
-        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C51" s="82"/>
       <c r="D51" s="82" t="s">
         <v>1011</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F51" s="51" t="str">
         <f t="shared" ref="F51:F62" si="11">SUBSTITUTE(E51, "hazr-", "")&amp;"-pb"&amp;H51</f>
@@ -46779,22 +46478,19 @@
       <c r="B52" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="82" t="str" cm="1">
-        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
-        <v>IF</v>
-      </c>
+      <c r="C52" s="82"/>
       <c r="D52" s="82" t="s">
         <v>1011</v>
       </c>
       <c r="E52" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F52" s="51" t="str">
         <f t="shared" ref="F52" si="12">SUBSTITUTE(E52, "hazr-", "")&amp;"-pb"&amp;H52</f>
         <v>p-if-proxy-lb-pb8080</v>
       </c>
       <c r="G52" s="82" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H52" s="82">
         <v>8080</v>
@@ -46805,7 +46501,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C53" s="102"/>
       <c r="D53" s="102" t="s">
@@ -46822,7 +46518,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I53" s="102"/>
       <c r="J53" s="102">
@@ -46834,14 +46530,14 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C54" s="102"/>
       <c r="D54" s="102" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F54" s="107" t="str">
         <f t="shared" si="11"/>
@@ -46851,7 +46547,7 @@
         <v>57</v>
       </c>
       <c r="H54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I54" s="102"/>
       <c r="J54" s="102">
@@ -46863,7 +46559,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C55" s="102"/>
       <c r="D55" s="102" t="s">
@@ -46880,7 +46576,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I55" s="102"/>
       <c r="J55" s="102">
@@ -46892,14 +46588,14 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C56" s="102"/>
       <c r="D56" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F56" s="107" t="str">
         <f t="shared" si="11"/>
@@ -46909,7 +46605,7 @@
         <v>57</v>
       </c>
       <c r="H56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I56" s="102"/>
       <c r="J56" s="102">
@@ -46921,7 +46617,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
@@ -46938,7 +46634,7 @@
         <v>57</v>
       </c>
       <c r="H57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I57" s="102"/>
       <c r="J57" s="102">
@@ -46950,14 +46646,14 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F58" s="107" t="str">
         <f t="shared" si="11"/>
@@ -46967,7 +46663,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I58" s="102"/>
       <c r="J58" s="102">
@@ -47112,12 +46808,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -47261,6 +46951,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -47271,22 +46967,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47304,6 +46984,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
